--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/VARILLA ROSCADA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/VARILLA ROSCADA DISMAY.xlsx
@@ -851,15 +851,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45211.54073725991</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -898,19 +895,6 @@
     <row r="11" ht="36.75" customHeight="1" s="16">
       <c r="A11" s="3" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="13.5" customHeight="1" s="16" thickBot="1"/>
     <row r="26" ht="15.75" customHeight="1" s="16" thickBot="1">
       <c r="A26" s="14" t="inlineStr">
@@ -947,7 +931,9 @@
         </is>
       </c>
       <c r="C27" s="20" t="n"/>
-      <c r="D27" s="6" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>233.496</v>
+      </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>200 Un.</t>
@@ -967,7 +953,7 @@
       </c>
       <c r="C28" s="20" t="n"/>
       <c r="D28" s="12" t="n">
-        <v>315.384</v>
+        <v>297.532</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
@@ -988,7 +974,7 @@
       </c>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="12" t="n">
-        <v>330.443</v>
+        <v>311.739</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -1009,7 +995,7 @@
       </c>
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="12" t="n">
-        <v>532.381</v>
+        <v>502.246</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -1030,7 +1016,7 @@
       </c>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="12" t="n">
-        <v>755.974</v>
+        <v>713.183</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -1051,7 +1037,7 @@
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="12" t="n">
-        <v>1056.284</v>
+        <v>996.494</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -1072,7 +1058,7 @@
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="12" t="n">
-        <v>1355.656</v>
+        <v>1278.921</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -1093,7 +1079,7 @@
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="12" t="n">
-        <v>2118.213</v>
+        <v>1998.314</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -1101,7 +1087,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="15.75" customHeight="1" s="16">
       <c r="A36" s="15" t="inlineStr">
         <is>
@@ -1109,11 +1094,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
@@ -1123,19 +1103,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
